--- a/artfynd/A 44426-2021 artfynd.xlsx
+++ b/artfynd/A 44426-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123913492</v>
+        <v>123913490</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465749</v>
+        <v>465741</v>
       </c>
       <c r="R2" t="n">
-        <v>6798363</v>
+        <v>6798376</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123913490</v>
+        <v>123913492</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465741</v>
+        <v>465749</v>
       </c>
       <c r="R3" t="n">
-        <v>6798376</v>
+        <v>6798363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 44426-2021 artfynd.xlsx
+++ b/artfynd/A 44426-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123913490</v>
+        <v>123913492</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465741</v>
+        <v>465749</v>
       </c>
       <c r="R2" t="n">
-        <v>6798376</v>
+        <v>6798363</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123913492</v>
+        <v>123913490</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465749</v>
+        <v>465741</v>
       </c>
       <c r="R3" t="n">
-        <v>6798363</v>
+        <v>6798376</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 44426-2021 artfynd.xlsx
+++ b/artfynd/A 44426-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123913490</v>
+        <v>123913492</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465741</v>
+        <v>465749</v>
       </c>
       <c r="R2" t="n">
-        <v>6798376</v>
+        <v>6798363</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123913492</v>
+        <v>123913490</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465749</v>
+        <v>465741</v>
       </c>
       <c r="R3" t="n">
-        <v>6798363</v>
+        <v>6798376</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 44426-2021 artfynd.xlsx
+++ b/artfynd/A 44426-2021 artfynd.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 44426-2021 artfynd.xlsx
+++ b/artfynd/A 44426-2021 artfynd.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson</t>
+          <t>Philipp Weiss, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 44426-2021 artfynd.xlsx
+++ b/artfynd/A 44426-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123913492</v>
+        <v>123913490</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465749</v>
+        <v>465741</v>
       </c>
       <c r="R2" t="n">
-        <v>6798363</v>
+        <v>6798376</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123913490</v>
+        <v>123913492</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465741</v>
+        <v>465749</v>
       </c>
       <c r="R3" t="n">
-        <v>6798376</v>
+        <v>6798363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
